--- a/artfynd/A 54614-2021 artfynd.xlsx
+++ b/artfynd/A 54614-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54614-2021 artfynd.xlsx
+++ b/artfynd/A 54614-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>73656955</v>
       </c>
       <c r="B2" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573213.1240570452</v>
+        <v>573213</v>
       </c>
       <c r="R2" t="n">
-        <v>6526680.204179361</v>
+        <v>6526680</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +745,9 @@
           <t>2018-10-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,55 +785,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73656301</v>
+        <v>84983075</v>
       </c>
       <c r="B3" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jakobsberg sö, Srm</t>
+          <t>Jakobsberg, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573323.0169579179</v>
+        <v>573182</v>
       </c>
       <c r="R3" t="n">
-        <v>6526650.224997099</v>
+        <v>6526639</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,85 +864,75 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>ängsartad kalkbarrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kryptogamer i Södermanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73656286</v>
+        <v>84983078</v>
       </c>
       <c r="B4" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jakobsberg so, Srm</t>
+          <t>Jakobsberg, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573301.0625186092</v>
+        <v>573199</v>
       </c>
       <c r="R4" t="n">
-        <v>6526605.846274713</v>
+        <v>6526624</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-10-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-10-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,66 +970,54 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kryptogamer i Södermanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>84983085</v>
+        <v>84983082</v>
       </c>
       <c r="B5" t="n">
-        <v>85301</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3739</v>
+        <v>445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1091,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573282.8510665861</v>
+        <v>573264</v>
       </c>
       <c r="R5" t="n">
-        <v>6526664.460532191</v>
+        <v>6526686</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,19 +1060,9 @@
           <t>2019-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,15 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84983083</v>
+        <v>73656286</v>
       </c>
       <c r="B6" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,40 +1104,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jakobsberg, Srm</t>
+          <t>Jakobsberg so, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573238.6968751904</v>
+        <v>573301</v>
       </c>
       <c r="R6" t="n">
-        <v>6526697.756637343</v>
+        <v>6526606</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,22 +1161,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,56 +1179,57 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kryptogamer i Södermanlands län</t>
-        </is>
-      </c>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>84983082</v>
+        <v>84983076</v>
       </c>
       <c r="B7" t="n">
-        <v>85177</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>445</v>
+        <v>3739</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1327,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573263.7833099861</v>
+        <v>573186</v>
       </c>
       <c r="R7" t="n">
-        <v>6526686.3375752</v>
+        <v>6526626</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1360,19 +1272,9 @@
           <t>2019-09-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,6 +1298,322 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kryptogamer i Södermanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>84983085</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87375</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Jakobsberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>573283</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6526664</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-09-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-09-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kryptogamer i Södermanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>73656301</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92497</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Jakobsberg sö, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>573323</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6526650</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-10-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-10-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>84983083</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jakobsberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>573239</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6526698</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-09-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-09-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Kryptogamer i Södermanlands län</t>
         </is>

--- a/artfynd/A 54614-2021 artfynd.xlsx
+++ b/artfynd/A 54614-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73656955</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84983075</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84983078</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Kryptogamer i Södermanlands län</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84983082</t>
         </is>
       </c>
     </row>
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73656286</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84983076</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84983085</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1513,6 +1553,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73656301</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1618,8 +1663,24 @@
           <t>Kryptogamer i Södermanlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84983083</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>